--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260902.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260902.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>6,022,000</t>
+          <t>6,089,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>4.14%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.81%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>21,637,000</t>
+          <t>6,254,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>6,066,000</t>
+          <t>21,637,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -704,73 +704,73 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>10,156,000</t>
+          <t>543,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>35,649,000</t>
+          <t>10,156,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>543,000</t>
+          <t>35,649,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
@@ -787,56 +787,56 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3,919,000</t>
+          <t>3,948,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>3,891,663,036</t>
+          <t>11,407,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>11,407,000</t>
+          <t>20,627,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>20,627,000</t>
+          <t>3,615,062,998</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
@@ -968,161 +968,161 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>36,304,000</t>
+          <t>9,588,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>9,588,000</t>
+          <t>36,304,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>4,345,000</t>
+          <t>32,953,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>32,953,000</t>
+          <t>2,217,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,217,000</t>
+          <t>9,548,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,883,000</t>
+          <t>4,345,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>9,548,000</t>
+          <t>2,883,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
@@ -1188,73 +1188,73 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,002,000</t>
+          <t>41,037,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,742,641,747</t>
+          <t>18,002,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>41,037,000</t>
+          <t>2,659,761,747</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -1276,24 +1276,24 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,179,000</t>
+          <t>4,984,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,984,000</t>
+          <t>6,179,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,44 +1327,44 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>9,652,000</t>
+          <t>7,883,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>7,883,000</t>
+          <t>9,652,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>14,405,000</t>
+          <t>3,901,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,22 +1415,22 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,901,000</t>
+          <t>14,405,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -1452,73 +1452,73 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>16,642,000</t>
+          <t>9,303,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>9,303,000</t>
+          <t>15,340,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>15,340,000</t>
+          <t>16,642,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1584,46 +1584,46 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,586,000</t>
+          <t>52,656,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>52,656,000</t>
+          <t>18,852,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,66 +1635,66 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>18,852,000</t>
+          <t>48,160,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>48,160,000</t>
+          <t>6,733,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>6,733,000</t>
+          <t>1,586,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
